--- a/data/obx_xlsx/SCATC.OL.xlsx
+++ b/data/obx_xlsx/SCATC.OL.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="396">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -717,43 +717,46 @@
     <t>Derivative Liabilities - Hedging - Long-Term</t>
   </si>
   <si>
+    <t>Other interest-bearing liabilities LT</t>
+  </si>
+  <si>
+    <t>Other Non-Current Liabilities</t>
+  </si>
+  <si>
+    <t>Shareholder loan from co-investors</t>
+  </si>
+  <si>
+    <t>Non-current lease liability</t>
+  </si>
+  <si>
+    <t>Asset Retirement Obligation</t>
+  </si>
+  <si>
+    <t>Other long-term liabilites and accruals</t>
+  </si>
+  <si>
+    <t>Balancing Item - Noncurrent Liabilities</t>
+  </si>
+  <si>
+    <t>Total Non-current Liabilities</t>
+  </si>
+  <si>
+    <t>Corporate financing</t>
+  </si>
+  <si>
+    <t>Current non-recourse project financing</t>
+  </si>
+  <si>
+    <t>Income Tax Payable</t>
+  </si>
+  <si>
+    <t>Trade payables and supplier finance</t>
+  </si>
+  <si>
+    <t>Derivative Liabilities - Hedging - Short-Term</t>
+  </si>
+  <si>
     <t>Other interest-bearing liabilities</t>
-  </si>
-  <si>
-    <t>Other Non-Current Liabilities</t>
-  </si>
-  <si>
-    <t>Shareholder loan from co-investors</t>
-  </si>
-  <si>
-    <t>Non-current lease liability</t>
-  </si>
-  <si>
-    <t>Asset Retirement Obligation</t>
-  </si>
-  <si>
-    <t>Other long-term liabilites and accruals</t>
-  </si>
-  <si>
-    <t>Balancing Item - Noncurrent Liabilities</t>
-  </si>
-  <si>
-    <t>Total Non-current Liabilities</t>
-  </si>
-  <si>
-    <t>Corporate financing</t>
-  </si>
-  <si>
-    <t>Current non-recourse project financing</t>
-  </si>
-  <si>
-    <t>Income Tax Payable</t>
-  </si>
-  <si>
-    <t>Trade payables and supplier finance</t>
-  </si>
-  <si>
-    <t>Derivative Liabilities - Hedging - Short-Term</t>
   </si>
   <si>
     <t>Other Current Liabilities</t>
@@ -10183,7 +10186,7 @@
       <c r="P93" s="16"/>
     </row>
     <row r="94" ht="15.0" customHeight="1">
-      <c r="A94" s="14" t="s">
+      <c r="A94" s="27" t="s">
         <v>232</v>
       </c>
       <c r="B94" s="15">
@@ -10667,8 +10670,8 @@
       <c r="P106" s="16"/>
     </row>
     <row r="107" ht="15.0" customHeight="1">
-      <c r="A107" s="14" t="s">
-        <v>232</v>
+      <c r="A107" s="27" t="s">
+        <v>245</v>
       </c>
       <c r="B107" s="15">
         <v>449.0</v>
@@ -10696,7 +10699,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B108" s="15">
         <v>2617.0</v>
@@ -10746,7 +10749,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B109" s="16"/>
       <c r="C109" s="20">
@@ -10784,7 +10787,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B110" s="16"/>
       <c r="C110" s="15">
@@ -10824,7 +10827,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B111" s="16"/>
       <c r="C111" s="16"/>
@@ -10862,7 +10865,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B112" s="16"/>
       <c r="C112" s="20">
@@ -10888,7 +10891,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B113" s="16"/>
       <c r="C113" s="16"/>
@@ -10912,7 +10915,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B114" s="16"/>
       <c r="C114" s="20">
@@ -10938,7 +10941,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B115" s="16"/>
       <c r="C115" s="16"/>
@@ -10964,7 +10967,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B116" s="16"/>
       <c r="C116" s="15">
@@ -11004,7 +11007,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B117" s="16"/>
       <c r="C117" s="20">
@@ -11026,7 +11029,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B118" s="16">
         <v>0.0</v>
@@ -11052,7 +11055,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B119" s="17">
         <v>-2.0</v>
@@ -11084,7 +11087,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B120" s="19">
         <v>6707.0</v>
@@ -11134,7 +11137,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B121" s="16"/>
       <c r="C121" s="16"/>
@@ -11156,7 +11159,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="18" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B122" s="23">
         <v>38069.0</v>
@@ -11206,7 +11209,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B123" s="16"/>
       <c r="C123" s="16"/>
@@ -11232,7 +11235,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="18" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B124" s="23">
         <v>50170.0</v>
@@ -11282,7 +11285,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B125" s="15">
         <v>158.92</v>
@@ -11332,7 +11335,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B126" s="16">
         <v>0.0</v>
@@ -11382,7 +11385,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B127" s="15">
         <v>158.92</v>
@@ -11432,7 +11435,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B128" s="16"/>
       <c r="C128" s="15">
@@ -11458,7 +11461,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B129" s="16"/>
       <c r="C129" s="15">
@@ -11484,7 +11487,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B130" s="16"/>
       <c r="C130" s="20">
@@ -11510,7 +11513,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B131" s="16"/>
       <c r="C131" s="20">
@@ -11536,7 +11539,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B132" s="16"/>
       <c r="C132" s="20">
@@ -11562,7 +11565,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B133" s="16"/>
       <c r="C133" s="20">
@@ -11588,7 +11591,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B134" s="16"/>
       <c r="C134" s="20">
@@ -11614,7 +11617,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B135" s="16"/>
       <c r="C135" s="15">
@@ -11640,7 +11643,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B136" s="16"/>
       <c r="C136" s="20">
@@ -11662,7 +11665,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B137" s="15">
         <v>158.92</v>
@@ -11712,7 +11715,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B138" s="15">
         <v>158.92</v>
@@ -11762,7 +11765,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B139" s="16">
         <v>0.0</v>
@@ -11812,7 +11815,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B140" s="20">
         <v>1.0</v>
@@ -11862,7 +11865,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B141" s="16"/>
       <c r="C141" s="15">
@@ -11892,7 +11895,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B142" s="16"/>
       <c r="C142" s="16"/>
@@ -11918,7 +11921,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B143" s="16"/>
       <c r="C143" s="16"/>
@@ -11944,7 +11947,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B144" s="16"/>
       <c r="C144" s="16"/>
@@ -11970,7 +11973,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B145" s="16"/>
       <c r="C145" s="16"/>
@@ -11996,7 +11999,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B146" s="16"/>
       <c r="C146" s="16"/>
@@ -12022,7 +12025,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B147" s="16"/>
       <c r="C147" s="16">
@@ -12937,7 +12940,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -13232,49 +13235,49 @@
         <v>37</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -13299,7 +13302,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -13419,7 +13422,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B21" s="15">
         <v>1168.0</v>
@@ -13489,7 +13492,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B23" s="24">
         <v>-964.0</v>
@@ -13539,7 +13542,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B24" s="24">
         <v>-645.0</v>
@@ -13565,7 +13568,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B25" s="24">
         <v>-159.0</v>
@@ -13615,7 +13618,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B26" s="16">
         <v>0.0</v>
@@ -13651,7 +13654,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -13695,7 +13698,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -13739,7 +13742,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -13781,7 +13784,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -13817,7 +13820,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B31" s="17">
         <v>-68.0</v>
@@ -13843,7 +13846,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B32" s="17">
         <v>-12.0</v>
@@ -13869,7 +13872,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B33" s="15">
         <v>294.0</v>
@@ -13903,7 +13906,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -13939,7 +13942,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -13975,7 +13978,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -14009,7 +14012,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -14043,7 +14046,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -14065,7 +14068,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
@@ -14111,7 +14114,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B41" s="20">
         <v>1.0</v>
@@ -14143,7 +14146,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="18" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B42" s="19">
         <v>2460.0</v>
@@ -14193,7 +14196,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -14215,7 +14218,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B44" s="24">
         <v>-6029.0</v>
@@ -14265,7 +14268,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -14289,7 +14292,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B46" s="15">
         <v>1965.0</v>
@@ -14319,7 +14322,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -14341,7 +14344,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B48" s="15">
         <v>1150.0</v>
@@ -14369,7 +14372,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B49" s="17">
         <v>-34.0</v>
@@ -14419,7 +14422,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B50" s="15">
         <v>201.0</v>
@@ -14469,7 +14472,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="17">
@@ -14499,7 +14502,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B52" s="25">
         <v>-2747.0</v>
@@ -14549,7 +14552,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
@@ -14585,7 +14588,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B54" s="15">
         <v>5425.0</v>
@@ -14633,7 +14636,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B55" s="15">
         <v>2225.0</v>
@@ -14659,7 +14662,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B56" s="15">
         <v>2118.0</v>
@@ -14685,7 +14688,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B57" s="16"/>
       <c r="C57" s="15">
@@ -14709,7 +14712,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B58" s="24">
         <v>-1155.0</v>
@@ -14757,7 +14760,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
@@ -14781,7 +14784,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B60" s="17">
         <v>-24.0</v>
@@ -14813,7 +14816,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B61" s="17">
         <v>-25.0</v>
@@ -14847,7 +14850,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
@@ -14875,7 +14878,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -14901,7 +14904,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B64" s="24">
         <v>-3782.0</v>
@@ -14927,7 +14930,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B65" s="24">
         <v>-523.0</v>
@@ -14949,7 +14952,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B66" s="24">
         <v>-2055.0</v>
@@ -14997,7 +15000,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="24">
@@ -15021,7 +15024,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B68" s="24">
         <v>-166.0</v>
@@ -15065,7 +15068,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -15101,7 +15104,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B70" s="15">
         <v>161.0</v>
@@ -15149,7 +15152,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B71" s="17">
         <v>-59.0</v>
@@ -15177,7 +15180,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
@@ -15199,7 +15202,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
@@ -15223,7 +15226,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B74" s="15">
         <v>143.0</v>
@@ -15251,7 +15254,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B75" s="16"/>
       <c r="C75" s="20">
@@ -15281,7 +15284,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B76" s="19">
         <v>2283.0</v>
@@ -15331,7 +15334,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B77" s="16">
         <v>0.0</v>
@@ -15357,7 +15360,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="18" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B78" s="23">
         <v>0.0</v>
@@ -15383,7 +15386,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B79" s="15">
         <v>5595.0</v>
@@ -15433,7 +15436,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B80" s="24">
         <v>-291.0</v>
@@ -15483,7 +15486,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B81" s="15">
         <v>1996.0</v>
@@ -15533,7 +15536,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B82" s="15">
         <v>3890.0</v>
@@ -15583,7 +15586,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="18" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B83" s="19">
         <v>1705.0</v>
@@ -16570,7 +16573,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -16915,7 +16918,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -16981,7 +16984,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="28" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -17000,7 +17003,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="30" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B21" s="31">
         <v>40037.92</v>
@@ -17041,7 +17044,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B22" s="31">
         <v>42595.03</v>
@@ -17074,7 +17077,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="28" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -17093,7 +17096,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="30" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B24" s="31">
         <v>12633.92</v>
@@ -17134,7 +17137,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="30" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B25" s="31">
         <v>23300.43</v>
@@ -17167,7 +17170,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="28" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B26" s="29"/>
       <c r="C26" s="29"/>
@@ -17186,7 +17189,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B27" s="33">
         <v>79.5</v>
@@ -17227,7 +17230,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B28" s="32">
         <v>146.88</v>
@@ -17260,7 +17263,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="28" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -17279,7 +17282,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="30" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B30" s="34">
         <v>-18.33</v>
@@ -17320,7 +17323,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="30" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B31" s="34">
         <v>-10.87</v>
@@ -17353,7 +17356,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="28" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -17372,7 +17375,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="30" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B33" s="35">
         <v>0.0</v>
@@ -17413,7 +17416,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="30" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B34" s="35">
         <v>0.69</v>
@@ -17446,7 +17449,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="30" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B35" s="35">
         <v>0.0</v>
@@ -17487,7 +17490,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="30" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B36" s="35">
         <v>0.89</v>
@@ -17520,7 +17523,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="28" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
@@ -17539,7 +17542,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="30" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B38" s="33">
         <v>1.19</v>
@@ -17580,7 +17583,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="30" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B39" s="33">
         <v>2.56</v>
@@ -17613,7 +17616,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="28" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
@@ -17632,7 +17635,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="30" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B41" s="33">
         <v>1.25</v>
@@ -17673,7 +17676,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="30" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B42" s="33">
         <v>2.73</v>
@@ -17706,7 +17709,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="28" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
@@ -17725,7 +17728,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="30" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B44" s="33">
         <v>2.89</v>
@@ -17766,7 +17769,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="30" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B45" s="33">
         <v>6.85</v>
@@ -17799,7 +17802,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="28" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
@@ -17818,7 +17821,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="30" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B47" s="33">
         <v>4.8</v>
@@ -17857,7 +17860,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="30" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B48" s="33">
         <v>19.38</v>
@@ -17890,7 +17893,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="28" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B49" s="29"/>
       <c r="C49" s="29"/>
@@ -17909,7 +17912,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="30" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B50" s="33">
         <v>9.65</v>
@@ -17942,7 +17945,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="30" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B51" s="32">
         <v>271.29</v>
@@ -17971,7 +17974,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="28" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
@@ -17990,7 +17993,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="30" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B53" s="33">
         <v>8.68</v>
@@ -18025,7 +18028,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="30" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B54" s="33">
         <v>2.56</v>
@@ -18058,7 +18061,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="28" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B55" s="29"/>
       <c r="C55" s="29"/>
@@ -18077,7 +18080,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="30" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B56" s="33">
         <v>0.09</v>
@@ -18110,7 +18113,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="30" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B57" s="31"/>
       <c r="C57" s="31"/>
@@ -18131,7 +18134,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="28" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B58" s="29"/>
       <c r="C58" s="29"/>
@@ -18150,7 +18153,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="30" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B59" s="33">
         <v>9.17</v>
@@ -18191,7 +18194,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="30" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B60" s="33">
         <v>12.85</v>
@@ -18224,7 +18227,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="28" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B61" s="29"/>
       <c r="C61" s="29"/>
@@ -18243,7 +18246,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="30" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B62" s="33">
         <v>12.46</v>
@@ -18284,7 +18287,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="30" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B63" s="33">
         <v>18.54</v>
@@ -18317,7 +18320,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="28" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B64" s="29"/>
       <c r="C64" s="29"/>
@@ -18336,7 +18339,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="30" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B65" s="33">
         <v>42.01</v>
@@ -18373,7 +18376,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="30" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B66" s="33">
         <v>75.6</v>
